--- a/scripts/files/UNDEPOSITED_FUNDS_2025_TEST.xlsx
+++ b/scripts/files/UNDEPOSITED_FUNDS_2025_TEST.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="30">
   <si>
     <t>Transaction date</t>
   </si>
@@ -78,6 +78,30 @@
   <si>
     <t>23500031</t>
   </si>
+  <si>
+    <t>3NZM1DML</t>
+  </si>
+  <si>
+    <t>23500032</t>
+  </si>
+  <si>
+    <t>MLFKTKSI</t>
+  </si>
+  <si>
+    <t>23500037</t>
+  </si>
+  <si>
+    <t>6HRCLZEI</t>
+  </si>
+  <si>
+    <t>23500043</t>
+  </si>
+  <si>
+    <t>WOW19EBJ</t>
+  </si>
+  <si>
+    <t>23500054</t>
+  </si>
 </sst>
 </file>
 
@@ -105,15 +129,15 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="8.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -140,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -153,22 +177,31 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -549,48 +582,120 @@
       </c>
     </row>
     <row r="6" outlineLevel="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="6">
+        <v>90000.0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>580000.0</v>
+      </c>
     </row>
     <row r="7" outlineLevel="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="6">
+        <v>38000.0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>618000.0</v>
+      </c>
     </row>
     <row r="8" outlineLevel="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="6">
+        <v>150000.0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>768000.0</v>
+      </c>
     </row>
     <row r="9" outlineLevel="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="6">
+        <v>50000.0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>818000.0</v>
+      </c>
     </row>
     <row r="10" outlineLevel="1">
       <c r="A10" s="2"/>
@@ -14057,63 +14162,63 @@
       <c r="I1233" s="3"/>
     </row>
     <row r="1234">
-      <c r="A1234" s="4"/>
-      <c r="B1234" s="5"/>
-      <c r="C1234" s="5"/>
-      <c r="D1234" s="5"/>
-      <c r="E1234" s="5"/>
-      <c r="F1234" s="5"/>
-      <c r="G1234" s="5"/>
-      <c r="H1234" s="6"/>
-      <c r="I1234" s="5"/>
+      <c r="A1234" s="7"/>
+      <c r="B1234" s="8"/>
+      <c r="C1234" s="8"/>
+      <c r="D1234" s="8"/>
+      <c r="E1234" s="8"/>
+      <c r="F1234" s="8"/>
+      <c r="G1234" s="8"/>
+      <c r="H1234" s="9"/>
+      <c r="I1234" s="8"/>
     </row>
     <row r="1235">
-      <c r="A1235" s="5"/>
-      <c r="B1235" s="5"/>
-      <c r="C1235" s="5"/>
-      <c r="D1235" s="5"/>
-      <c r="E1235" s="5"/>
-      <c r="F1235" s="5"/>
-      <c r="G1235" s="7"/>
-      <c r="H1235" s="8"/>
-      <c r="I1235" s="5"/>
+      <c r="A1235" s="8"/>
+      <c r="B1235" s="8"/>
+      <c r="C1235" s="8"/>
+      <c r="D1235" s="8"/>
+      <c r="E1235" s="8"/>
+      <c r="F1235" s="8"/>
+      <c r="G1235" s="10"/>
+      <c r="H1235" s="11"/>
+      <c r="I1235" s="8"/>
     </row>
     <row r="1236">
-      <c r="A1236" s="5"/>
-      <c r="B1236" s="5"/>
-      <c r="C1236" s="5"/>
-      <c r="D1236" s="5"/>
-      <c r="E1236" s="5"/>
-      <c r="F1236" s="5"/>
-      <c r="G1236" s="9"/>
-      <c r="H1236" s="9"/>
-      <c r="I1236" s="5"/>
+      <c r="A1236" s="8"/>
+      <c r="B1236" s="8"/>
+      <c r="C1236" s="8"/>
+      <c r="D1236" s="8"/>
+      <c r="E1236" s="8"/>
+      <c r="F1236" s="8"/>
+      <c r="G1236" s="12"/>
+      <c r="H1236" s="12"/>
+      <c r="I1236" s="8"/>
     </row>
     <row r="1237">
-      <c r="A1237" s="5"/>
-      <c r="B1237" s="5"/>
-      <c r="C1237" s="5"/>
-      <c r="D1237" s="5"/>
-      <c r="E1237" s="5"/>
-      <c r="F1237" s="5"/>
-      <c r="G1237" s="5"/>
-      <c r="H1237" s="5"/>
-      <c r="I1237" s="5"/>
+      <c r="A1237" s="8"/>
+      <c r="B1237" s="8"/>
+      <c r="C1237" s="8"/>
+      <c r="D1237" s="8"/>
+      <c r="E1237" s="8"/>
+      <c r="F1237" s="8"/>
+      <c r="G1237" s="8"/>
+      <c r="H1237" s="8"/>
+      <c r="I1237" s="8"/>
     </row>
     <row r="1238">
-      <c r="A1238" s="5"/>
-      <c r="B1238" s="5"/>
-      <c r="C1238" s="5"/>
-      <c r="D1238" s="5"/>
-      <c r="E1238" s="5"/>
-      <c r="F1238" s="5"/>
-      <c r="G1238" s="5"/>
-      <c r="H1238" s="5"/>
-      <c r="I1238" s="5"/>
+      <c r="A1238" s="8"/>
+      <c r="B1238" s="8"/>
+      <c r="C1238" s="8"/>
+      <c r="D1238" s="8"/>
+      <c r="E1238" s="8"/>
+      <c r="F1238" s="8"/>
+      <c r="G1238" s="8"/>
+      <c r="H1238" s="8"/>
+      <c r="I1238" s="8"/>
     </row>
     <row r="1239">
-      <c r="A1239" s="10"/>
-      <c r="I1239" s="5"/>
+      <c r="A1239" s="13"/>
+      <c r="I1239" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
